--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55411791-AB2A-4AB7-972E-998CEBC3B40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E713A938-1866-4422-ACEE-1E24A659B1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +220,12 @@
   </si>
   <si>
     <t>Feels like sleepe</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>The day was wast become the python lecture got cancel</t>
   </si>
 </sst>
 </file>
@@ -874,8 +879,11 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="35.88671875" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -932,7 +940,9 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20">
+        <v>8</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1149,7 +1159,7 @@
         <v>60</v>
       </c>
       <c r="E9" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F9" s="14">
         <v>420</v>
@@ -1162,11 +1172,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1110</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>56</v>
@@ -1181,29 +1191,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46254</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="B10" s="14">
+        <v>450</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>360</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E713A938-1866-4422-ACEE-1E24A659B1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF62290-2058-4EE8-979B-948977007647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>The day was wast become the python lecture got cancel</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>good day but the pressure  is increeseing</t>
   </si>
 </sst>
 </file>
@@ -1237,30 +1243,56 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B11" s="14">
+        <v>520</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>420</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>190</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13">
+        <v>47352</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF62290-2058-4EE8-979B-948977007647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE4A7B5-4D92-40B9-9CE7-37EEB3C356C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,18 @@
   </si>
   <si>
     <t>good day but the pressure  is increeseing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good </t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day was a west </t>
+  </si>
+  <si>
+    <t>2026-0825</t>
   </si>
 </sst>
 </file>
@@ -1291,74 +1303,146 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>47352</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>46256</v>
+      </c>
+      <c r="B12" s="14">
+        <v>520</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B13" s="14">
+        <v>550</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B14" s="14">
+        <v>390</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>240</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE4A7B5-4D92-40B9-9CE7-37EEB3C356C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2398B49-6161-4FF2-BDE3-9E06566C09E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">The day was a west </t>
   </si>
   <si>
-    <t>2026-0825</t>
+    <t>not feel like to study</t>
   </si>
 </sst>
 </file>
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E13" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F13" s="14">
         <v>0</v>
@@ -1374,11 +1374,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>670</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>770</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1404,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E14" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
         <v>240</v>
@@ -1420,11 +1420,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>830</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>610</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>49</v>
@@ -1440,89 +1440,157 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B15" s="14">
+        <v>400</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B16" s="14">
+        <v>380</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13">
+        <v>46261</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="F17" s="14">
+        <v>360</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>300</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46262</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+      <c r="F18" s="14">
+        <v>420</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
       <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2398B49-6161-4FF2-BDE3-9E06566C09E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792C02FC-37FF-450E-921F-9DE5B8E45723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1535,10 +1535,18 @@
       <c r="A17" s="13">
         <v>46261</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="14">
+        <v>400</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
       <c r="F17" s="14">
         <v>360</v>
       </c>
@@ -1550,11 +1558,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>1060</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>380</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1573,76 +1581,142 @@
       <c r="A18" s="13">
         <v>46262</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="B18" s="14">
+        <v>500</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
       <c r="F18" s="14">
         <v>420</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="14">
+        <v>400</v>
+      </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>1320</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B19" s="14">
+        <v>600</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>400</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46264</v>
+      </c>
       <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>400</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>920</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46265</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792C02FC-37FF-450E-921F-9DE5B8E45723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7149E0-06DA-433C-B64B-1C6205E1BCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>not feel like to study</t>
+  </si>
+  <si>
+    <t>try to do study</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1676,9 @@
       <c r="A20" s="13">
         <v>46264</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="14">
+        <v>500</v>
+      </c>
       <c r="C20" s="14">
         <v>0</v>
       </c>
@@ -1694,11 +1699,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>1020</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>920</v>
+        <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1718,27 +1723,49 @@
         <v>46265</v>
       </c>
       <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>120</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>400</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46266</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>

--- a/12620127.xlsx
+++ b/12620127.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily Routine LPU\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7149E0-06DA-433C-B64B-1C6205E1BCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7DE099-1D0D-45CE-B753-86BEBAA7C21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1722,7 +1722,9 @@
       <c r="A21" s="13">
         <v>46265</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="14">
+        <v>500</v>
+      </c>
       <c r="C21" s="14">
         <v>0</v>
       </c>
@@ -1743,11 +1745,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>640</v>
+        <v>1140</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
@@ -1767,27 +1769,49 @@
         <v>46266</v>
       </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46267</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
